--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87097</v>
+        <v>87099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87099</v>
+        <v>87101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87101</v>
+        <v>87103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87103</v>
+        <v>87105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87105</v>
+        <v>87107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87107</v>
+        <v>87108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87108</v>
+        <v>87114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>446345</v>
+        <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>88422</v>
+        <v>91551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1164,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1007</v>
+        <v>688</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stäppröksvamp</t>
+          <t>Dvärgjordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycoperdon decipiens</t>
+          <t>Geastrum schmidelii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Durieu &amp; Mont.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Vittad.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, gamla järnvägsvallen, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601117</v>
+        <v>601057</v>
       </c>
       <c r="R6" t="n">
-        <v>6276566</v>
+        <v>6276540</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-03-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-03-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,30 +1243,36 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>betad sandgräshed, längs norra muren</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/446345</t>
+          <t>https://artportalen.se/Sighting/137226892</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>446346</v>
+        <v>446345</v>
       </c>
       <c r="B7" t="n">
         <v>88422</v>
@@ -1286,14 +1303,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dörby, längs jvgs-vallen genom tallskogen ml. sandheden och D. gravfäl, Öl</t>
+          <t>Gårdby sandstäpp, gamla järnvägsvallen, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601115</v>
+        <v>601117</v>
       </c>
       <c r="R7" t="n">
-        <v>6276569</v>
+        <v>6276566</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,11 +1345,6 @@
           <t>2005-03-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Leg. U-B. Andersson &amp; Th. Gunnarsson</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1342,40 +1354,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Längs gammal järnvägsvall.</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Tommy Knutsson - Import Fynddatabas 2013</t>
-        </is>
-      </c>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/446346</t>
+          <t>https://artportalen.se/Sighting/446345</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>308352</v>
+        <v>446346</v>
       </c>
       <c r="B8" t="n">
-        <v>111369</v>
+        <v>88422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,46 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1188</v>
+        <v>1007</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backsilja</t>
+          <t>Stäppröksvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Peucedanum oreoselinum</t>
+          <t>Lycoperdon decipiens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Durieu &amp; Mont.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdby sandhed vägren 2, Öl</t>
+          <t>Dörby, längs jvgs-vallen genom tallskogen ml. sandheden och D. gravfäl, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601160</v>
+        <v>601115</v>
       </c>
       <c r="R8" t="n">
-        <v>6276529</v>
+        <v>6276569</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,19 +1437,19 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Hö-Mör-9124</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2005-03-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2005-03-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Leg. U-B. Andersson &amp; Th. Gunnarsson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,83 +1461,87 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Längs gammal järnvägsvall.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Via Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+          <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/308352</t>
+          <t>https://artportalen.se/Sighting/446346</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123412399</v>
+        <v>308352</v>
       </c>
       <c r="B9" t="n">
-        <v>86926</v>
+        <v>111369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1615</v>
+        <v>1188</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk stjälkröksvamp</t>
+          <t>Backsilja</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tulostoma melanocyclum</t>
+          <t>Peucedanum oreoselinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed vägren 2, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601049</v>
+        <v>601160</v>
       </c>
       <c r="R9" t="n">
-        <v>6276539</v>
+        <v>6276529</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,17 +1560,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Hö-Mör-9124</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,36 +1584,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>betad sandstäpp</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Öland- Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412399</t>
+          <t>https://artportalen.se/Sighting/308352</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124946770</v>
+        <v>123412399</v>
       </c>
       <c r="B10" t="n">
         <v>86926</v>
@@ -1639,20 +1639,28 @@
           <t>Bres.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601035</v>
+        <v>601049</v>
       </c>
       <c r="R10" t="n">
-        <v>6276550</v>
+        <v>6276539</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,12 +1687,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,7 +1707,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>betad sandgräshed</t>
+          <t>betad sandstäpp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1710,22 +1718,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946770</t>
+          <t>https://artportalen.se/Sighting/123412399</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132868082</v>
+        <v>124946770</v>
       </c>
       <c r="B11" t="n">
-        <v>86988</v>
+        <v>86926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,28 +1758,20 @@
           <t>Bres.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed NR, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601052</v>
+        <v>601035</v>
       </c>
       <c r="R11" t="n">
-        <v>6276541</v>
+        <v>6276550</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132868082</t>
+          <t>https://artportalen.se/Sighting/124946770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136475997</v>
+        <v>132868082</v>
       </c>
       <c r="B12" t="n">
-        <v>87114</v>
+        <v>86988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1883,14 +1883,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gårdby sandhed , Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601055</v>
+        <v>601052</v>
       </c>
       <c r="R12" t="n">
-        <v>6276536</v>
+        <v>6276541</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1917,17 +1917,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,16 +1954,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136475997</t>
+          <t>https://artportalen.se/Sighting/132868082</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>635973</v>
+        <v>136475997</v>
       </c>
       <c r="B13" t="n">
-        <v>100693</v>
+        <v>87114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,37 +1971,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1888</v>
+        <v>1615</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Mörk stjälkröksvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Tulostoma melanocyclum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Bres.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gårdby sandhed (16), Öl</t>
+          <t>Gårdby sandhed , Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601043</v>
+        <v>601055</v>
       </c>
       <c r="R13" t="n">
-        <v>6276537</v>
+        <v>6276536</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2028,19 +2034,19 @@
           <t>Gårdby</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Hö-Mör-0159</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,39 +2055,36 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>sandstäpp</t>
+          <t>betad sandgräshed</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Öland- Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/635973</t>
+          <t>https://artportalen.se/Sighting/136475997</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54136158</v>
+        <v>635973</v>
       </c>
       <c r="B14" t="n">
         <v>100693</v>
@@ -2110,23 +2113,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO., Öl</t>
+          <t>Gårdby sandhed (16), Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601088</v>
+        <v>601043</v>
       </c>
       <c r="R14" t="n">
-        <v>6276505</v>
+        <v>6276537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,14 +2147,19 @@
           <t>Gårdby</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Hö-Mör-0159</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,85 +2171,84 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Sandstäpp</t>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Via Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54136158</t>
+          <t>https://artportalen.se/Sighting/635973</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124946789</v>
+        <v>54136158</v>
       </c>
       <c r="B15" t="n">
-        <v>100795</v>
+        <v>100693</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1900</v>
+        <v>1888</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sandtimotej</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phleum arenarium</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR, Öl</t>
+          <t>Gårdby sandhed NO., Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601035</v>
+        <v>601088</v>
       </c>
       <c r="R15" t="n">
-        <v>6276550</v>
+        <v>6276505</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,36 +2286,39 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>betad sandgräshed</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Sandstäpp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heléne Wertwein Haavikko, Stefan Svenaeus, Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946789</t>
+          <t>https://artportalen.se/Sighting/54136158</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125168508</v>
+        <v>124946789</v>
       </c>
       <c r="B16" t="n">
         <v>100795</v>
@@ -2344,19 +2347,27 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gårdby sandheds naturreservat, Öl</t>
+          <t>Gårdby sandhed NR, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601069</v>
+        <v>601035</v>
       </c>
       <c r="R16" t="n">
-        <v>6276520</v>
+        <v>6276550</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2380,12 +2391,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,74 +2405,77 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>betad sandgräshed</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen, Pontus Axén</t>
+          <t>Heléne Wertwein Haavikko, Stefan Svenaeus, Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125168508</t>
+          <t>https://artportalen.se/Sighting/124946789</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98135249</v>
+        <v>125168508</v>
       </c>
       <c r="B17" t="n">
-        <v>89085</v>
+        <v>100795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4379</v>
+        <v>1900</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Sandtimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Phleum arenarium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
+          <t>Gårdby sandheds naturreservat, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601111</v>
+        <v>601069</v>
       </c>
       <c r="R17" t="n">
-        <v>6276524</v>
+        <v>6276520</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,17 +2494,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1993-09-21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1993-09-21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,39 +2513,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>På kalkrik sand med sparsam Koeleria-veg. på gamla järnvägsvallen genom tallskogen.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Karl-göran Bringer</t>
+          <t>Janne Kolehmainen, Pontus Axén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98135249</t>
+          <t>https://artportalen.se/Sighting/125168508</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134635235</v>
+        <v>98135249</v>
       </c>
       <c r="B18" t="n">
-        <v>57921</v>
+        <v>89085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,37 +2547,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100067</v>
+        <v>4379</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601058</v>
+        <v>601111</v>
       </c>
       <c r="R18" t="n">
-        <v>6276542</v>
+        <v>6276524</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,12 +2604,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>1993-09-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>1993-09-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,93 +2618,77 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>sandstäpp</t>
+          <t>På kalkrik sand med sparsam Koeleria-veg. på gamla järnvägsvallen genom tallskogen.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Anders Källberg, Ann-Sofie Åsander, Christina Stenberg, Eva Grönlund, Gunnar Noren, Gunnel Ström, Karin Hendahl, Leif lagerstedt, Margareta Danielsson, Patrik Engström, Per Johnsson, Rolf Wahlström, Susanne Rosengren, Lisa Lundin</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>BSIS-exkursion</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson, Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134635235</t>
+          <t>https://artportalen.se/Sighting/98135249</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>78876850</v>
+        <v>134635235</v>
       </c>
       <c r="B19" t="n">
-        <v>43908</v>
+        <v>57921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100370</v>
+        <v>100067</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skiktdynemott</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Apomyelois bistriatella</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hulst, 1887)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601040</v>
+        <v>601058</v>
       </c>
       <c r="R19" t="n">
-        <v>6276621</v>
+        <v>6276542</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,22 +2712,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>02:30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,34 +2726,42 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Anders Källberg, Ann-Sofie Åsander, Christina Stenberg, Eva Grönlund, Gunnar Noren, Gunnel Ström, Karin Hendahl, Leif lagerstedt, Margareta Danielsson, Patrik Engström, Per Johnsson, Rolf Wahlström, Susanne Rosengren, Lisa Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>BSIS-exkursion</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876850</t>
+          <t>https://artportalen.se/Sighting/134635235</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67263366</v>
+        <v>78876850</v>
       </c>
       <c r="B20" t="n">
-        <v>44113</v>
+        <v>43908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,21 +2769,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100437</v>
+        <v>100370</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klocksäckspinnare</t>
+          <t>Skiktdynemott</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bacotia claustrella</t>
+          <t>Apomyelois bistriatella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bruand, 1845)</t>
+          <t>(Hulst, 1887)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2799,31 +2792,27 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>bankning</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601087</v>
+        <v>601040</v>
       </c>
       <c r="R20" t="n">
-        <v>6276560</v>
+        <v>6276621</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2847,12 +2836,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,55 +2860,56 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67263366</t>
+          <t>https://artportalen.se/Sighting/78876850</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>78876254</v>
+        <v>67263366</v>
       </c>
       <c r="B21" t="n">
-        <v>41689</v>
+        <v>44113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100562</v>
+        <v>100437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbandad fältmätare</t>
+          <t>Klocksäckspinnare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Catarhoe rubidata</t>
+          <t>Bacotia claustrella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Bruand, 1845)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2918,27 +2918,31 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>bankning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>N Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601040</v>
+        <v>601087</v>
       </c>
       <c r="R21" t="n">
-        <v>6276621</v>
+        <v>6276560</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,22 +2966,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>02:30</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,34 +2980,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876254</t>
+          <t>https://artportalen.se/Sighting/67263366</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877763</v>
+        <v>78876254</v>
       </c>
       <c r="B22" t="n">
-        <v>8203</v>
+        <v>41689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3021,21 +3014,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100704</v>
+        <v>100562</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sandspolvivel</t>
+          <t>Rödbandad fältmätare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Coniocleonus turbatus</t>
+          <t>Catarhoe rubidata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fåhraeus, 1842)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3044,31 +3037,27 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601059</v>
+        <v>601040</v>
       </c>
       <c r="R22" t="n">
-        <v>6276518</v>
+        <v>6276621</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,17 +3076,27 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,49 +3112,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125877763</t>
+          <t>https://artportalen.se/Sighting/78876254</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14216453</v>
+        <v>125877763</v>
       </c>
       <c r="B23" t="n">
-        <v>9660</v>
+        <v>8203</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100708</v>
+        <v>100704</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Månhornsbagge</t>
+          <t>Sandspolvivel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copris lunaris</t>
+          <t>Coniocleonus turbatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fåhraeus, 1842)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3163,19 +3162,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gï¿½rdby Sand, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600994</v>
+        <v>601059</v>
       </c>
       <c r="R23" t="n">
-        <v>6276562</v>
+        <v>6276518</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,17 +3211,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2009-06-02</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2009-06-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Pï¿½ uppdrag av Lï¿½nsstyrelsen i Kalmar Lï¿½n</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,94 +3225,73 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>nï¿½tspillning sandig ljunghed</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Naturcentrum AB</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14216453</t>
+          <t>https://artportalen.se/Sighting/125877763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>70551999</v>
+        <v>14216453</v>
       </c>
       <c r="B24" t="n">
-        <v>41416</v>
+        <v>9660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101061</v>
+        <v>100708</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smaragdgrön lundmätare</t>
+          <t>Månhornsbagge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hemistola chrysoprasaria</t>
+          <t>Copris lunaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Esper, 1795)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>lampa</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gï¿½rdby Sand, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600995</v>
+        <v>600994</v>
       </c>
       <c r="R24" t="n">
-        <v>6276588</v>
+        <v>6276562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3327,17 +3313,22 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
+          <t>2009-06-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
+          <t>2009-06-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Pï¿½ uppdrag av Lï¿½nsstyrelsen i Kalmar Lï¿½n</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,58 +3339,67 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>nï¿½tspillning sandig ljunghed</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Naturcentrum AB</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Annette Bludau, Fred Ockruck</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70551999</t>
+          <t>https://artportalen.se/Sighting/14216453</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877437</v>
+        <v>70551999</v>
       </c>
       <c r="B25" t="n">
-        <v>8244</v>
+        <v>41416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101201</v>
+        <v>101061</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blyvivel</t>
+          <t>Smaragdgrön lundmätare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepyrus capucinus</t>
+          <t>Hemistola chrysoprasaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Esper, 1795)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3409,25 +3409,25 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601059</v>
+        <v>600995</v>
       </c>
       <c r="R25" t="n">
-        <v>6276518</v>
+        <v>6276588</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3446,17 +3446,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,34 +3465,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Annette Bludau, Fred Ockruck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125877437</t>
+          <t>https://artportalen.se/Sighting/70551999</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>91366160</v>
+        <v>125877437</v>
       </c>
       <c r="B26" t="n">
-        <v>13045</v>
+        <v>8244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,21 +3499,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101225</v>
+        <v>101201</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Öländsk svävfluga</t>
+          <t>Blyvivel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lomatia lateralis</t>
+          <t>Lepyrus capucinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Meigen, 1820)</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3522,29 +3521,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gårdby Sandstäpp, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601081</v>
+        <v>601059</v>
       </c>
       <c r="R26" t="n">
-        <v>6276523</v>
+        <v>6276518</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3563,17 +3565,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3582,48 +3584,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>sandstäpp</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>Erik Sjödin</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Personlig inventering NES</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91366160</t>
+          <t>https://artportalen.se/Sighting/125877437</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132686520</v>
+        <v>91366160</v>
       </c>
       <c r="B27" t="n">
-        <v>41740</v>
+        <v>13045</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,21 +3619,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101256</v>
+        <v>101225</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre purpurmätare</t>
+          <t>Öländsk svävfluga</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lythria cruentaria</t>
+          <t>Lomatia lateralis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Meigen, 1820)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3653,29 +3641,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601031</v>
+        <v>601081</v>
       </c>
       <c r="R27" t="n">
-        <v>6276536</v>
+        <v>6276523</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3697,27 +3682,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2020-07-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2020-07-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3726,56 +3701,70 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr"/>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Personlig inventering NES</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132686520</t>
+          <t>https://artportalen.se/Sighting/91366160</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125940660</v>
+        <v>132686520</v>
       </c>
       <c r="B28" t="n">
-        <v>30576</v>
+        <v>41740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101668</v>
+        <v>101256</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandgeting</t>
+          <t>Mindre purpurmätare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pterocheilus phaleratus</t>
+          <t>Lythria cruentaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Panzer, 1797)</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3798,17 +3787,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601044</v>
+        <v>601031</v>
       </c>
       <c r="R28" t="n">
-        <v>6276529</v>
+        <v>6276536</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3832,22 +3821,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,49 +3852,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Edvin Klein, Ove Grönlund, Simon Stenberg Jönsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125940660</t>
+          <t>https://artportalen.se/Sighting/132686520</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>94824102</v>
+        <v>125940660</v>
       </c>
       <c r="B29" t="n">
-        <v>42206</v>
+        <v>30576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101814</v>
+        <v>101668</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Streckhedspinnare</t>
+          <t>Sandgeting</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spiris striata</t>
+          <t>Pterocheilus phaleratus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Panzer, 1797)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3919,30 +3908,26 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601031</v>
+        <v>601044</v>
       </c>
       <c r="R29" t="n">
-        <v>6276536</v>
+        <v>6276529</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3966,12 +3951,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,44 +3982,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Jon Liljebäck, Edvin Klein, Ove Grönlund, Simon Stenberg Jönsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94824102</t>
+          <t>https://artportalen.se/Sighting/125940660</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132686496</v>
+        <v>94824102</v>
       </c>
       <c r="B30" t="n">
-        <v>29446</v>
+        <v>42206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102702</v>
+        <v>101814</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mosshumla</t>
+          <t>Streckhedspinnare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bombus muscorum</t>
+          <t>Spiris striata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4043,10 +4038,14 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4086,27 +4085,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På fältsippa</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4127,22 +4111,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132686496</t>
+          <t>https://artportalen.se/Sighting/94824102</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116368544</v>
+        <v>132686496</v>
       </c>
       <c r="B31" t="n">
-        <v>43435</v>
+        <v>29446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4150,16 +4134,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102922</v>
+        <v>102702</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ängsnätfjäril</t>
+          <t>Mosshumla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Melitaea cinxia</t>
+          <t>Bombus muscorum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4169,35 +4153,35 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gårdby sandheds naturreservat, Gårdby sandheds naturreservat, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601036</v>
+        <v>601031</v>
       </c>
       <c r="R31" t="n">
-        <v>6276538</v>
+        <v>6276536</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4221,27 +4205,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Larverna spridda på någon m2.</t>
+          <t>På fältsippa</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4257,24 +4241,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116368544</t>
+          <t>https://artportalen.se/Sighting/132686496</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117088512</v>
+        <v>116368544</v>
       </c>
       <c r="B32" t="n">
         <v>43435</v>
@@ -4304,35 +4288,35 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandheds naturreservat, Gårdby sandheds naturreservat, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601031</v>
+        <v>601036</v>
       </c>
       <c r="R32" t="n">
-        <v>6276536</v>
+        <v>6276538</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4356,12 +4340,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Larverna spridda på någon m2.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4377,27 +4376,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117088512</t>
+          <t>https://artportalen.se/Sighting/116368544</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>81631800</v>
+        <v>117088512</v>
       </c>
       <c r="B33" t="n">
-        <v>58586</v>
+        <v>43435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,49 +4404,54 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103051</v>
+        <v>102922</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Ängsnätfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Melitaea cinxia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601111</v>
+        <v>601031</v>
       </c>
       <c r="R33" t="n">
-        <v>6276524</v>
+        <v>6276536</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4466,17 +4470,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1987-05-28</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1987-05-28</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4485,33 +4489,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81631800</t>
+          <t>https://artportalen.se/Sighting/117088512</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102089937</v>
+        <v>81631800</v>
       </c>
       <c r="B34" t="n">
-        <v>43310</v>
+        <v>58586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,21 +4524,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>201145</v>
+        <v>103051</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Väpplingblåvinge</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polyommatus dorylas</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4541,36 +4546,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601031</v>
+        <v>601111</v>
       </c>
       <c r="R34" t="n">
-        <v>6276536</v>
+        <v>6276524</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4589,27 +4585,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>1987-05-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>1987-05-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4618,34 +4604,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089937</t>
+          <t>https://artportalen.se/Sighting/81631800</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101765495</v>
+        <v>102089937</v>
       </c>
       <c r="B35" t="n">
-        <v>41060</v>
+        <v>43310</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4653,16 +4638,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>214757</v>
+        <v>201145</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bågstreckad näbbmal</t>
+          <t>Väpplingblåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sophronia humerella</t>
+          <t>Polyommatus dorylas</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4670,29 +4655,41 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601080</v>
+        <v>601031</v>
       </c>
       <c r="R35" t="n">
-        <v>6276524</v>
+        <v>6276536</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4711,17 +4708,27 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4737,86 +4744,74 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765495</t>
+          <t>https://artportalen.se/Sighting/102089937</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97292096</v>
+        <v>101765495</v>
       </c>
       <c r="B36" t="n">
-        <v>44833</v>
+        <v>41060</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214907</v>
+        <v>214757</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Större vitbandsvecklare</t>
+          <t>Bågstreckad näbbmal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Xerocnephasia rigana</t>
+          <t>Sophronia humerella</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sodoffsky, 1829)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR N, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601106</v>
+        <v>601080</v>
       </c>
       <c r="R36" t="n">
-        <v>6276509</v>
+        <v>6276524</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4840,27 +4835,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:32</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>vid parkeringen</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4873,60 +4853,59 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Sandgräsmark</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97292096</t>
+          <t>https://artportalen.se/Sighting/101765495</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101765511</v>
+        <v>97292096</v>
       </c>
       <c r="B37" t="n">
-        <v>44549</v>
+        <v>44833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>215095</v>
+        <v>214907</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Månskärerotvecklare</t>
+          <t>Större vitbandsvecklare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelochrista huebneriana</t>
+          <t>Xerocnephasia rigana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lienig &amp; Zeller, 1846)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Sodoffsky, 1829)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -4934,25 +4913,29 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed NR N, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601080</v>
+        <v>601106</v>
       </c>
       <c r="R37" t="n">
-        <v>6276524</v>
+        <v>6276509</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4976,12 +4959,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>vid parkeringen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4994,27 +4992,32 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Sandgräsmark</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Kaj Svahn</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765511</t>
+          <t>https://artportalen.se/Sighting/97292096</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111101304</v>
+        <v>101765511</v>
       </c>
       <c r="B38" t="n">
         <v>44549</v>
@@ -5042,11 +5045,7 @@
           <t>(Lienig &amp; Zeller, 1846)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -5054,22 +5053,22 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, skogsvägen norr om, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601026</v>
+        <v>601080</v>
       </c>
       <c r="R38" t="n">
-        <v>6276537</v>
+        <v>6276524</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5091,27 +5090,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5127,27 +5116,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
+          <t>Jesper Hansson, Kaj Svahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111101304</t>
+          <t>https://artportalen.se/Sighting/101765511</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>78876826</v>
+        <v>111101304</v>
       </c>
       <c r="B39" t="n">
-        <v>43981</v>
+        <v>44549</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5155,46 +5144,54 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>215320</v>
+        <v>215095</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brokigt timjansmott</t>
+          <t>Månskärerotvecklare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pempeliella ornatella</t>
+          <t>Pelochrista huebneriana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Lienig &amp; Zeller, 1846)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandhed, skogsvägen norr om, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601040</v>
+        <v>601026</v>
       </c>
       <c r="R39" t="n">
-        <v>6276621</v>
+        <v>6276537</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5213,27 +5210,27 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5249,27 +5246,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876826</t>
+          <t>https://artportalen.se/Sighting/111101304</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>15750705</v>
+        <v>78876826</v>
       </c>
       <c r="B40" t="n">
-        <v>41758</v>
+        <v>43981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5277,33 +5274,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>215656</v>
+        <v>215320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Brokigt timjansmott</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Pempeliella ornatella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5311,17 +5303,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>600995</v>
+        <v>601040</v>
       </c>
       <c r="R40" t="n">
-        <v>6276588</v>
+        <v>6276621</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5345,12 +5337,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2013-07-29</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2013-07-30</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5359,30 +5361,31 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15750705</t>
+          <t>https://artportalen.se/Sighting/78876826</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17066601</v>
+        <v>15750705</v>
       </c>
       <c r="B41" t="n">
         <v>41758</v>
@@ -5412,21 +5415,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5434,17 +5430,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601075</v>
+        <v>600995</v>
       </c>
       <c r="R41" t="n">
-        <v>6276530</v>
+        <v>6276588</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5468,22 +5464,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2013-07-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5498,27 +5484,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Per Gustafsson, Tobias Hammarberg, David Hammarberg, Johan Södercrantz</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17066601</t>
+          <t>https://artportalen.se/Sighting/15750705</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>70430543</v>
+        <v>17066601</v>
       </c>
       <c r="B42" t="n">
-        <v>41451</v>
+        <v>41758</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5526,16 +5512,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>215683</v>
+        <v>215656</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5555,7 +5541,11 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5563,17 +5553,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>600995</v>
+        <v>601075</v>
       </c>
       <c r="R42" t="n">
-        <v>6276588</v>
+        <v>6276530</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5597,22 +5587,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2014-06-28</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5627,27 +5617,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Per Gustafsson, Tobias Hammarberg, David Hammarberg, Johan Södercrantz</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70430543</t>
+          <t>https://artportalen.se/Sighting/17066601</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>90973717</v>
+        <v>70430543</v>
       </c>
       <c r="B43" t="n">
-        <v>41695</v>
+        <v>41451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5655,39 +5645,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>215701</v>
+        <v>215683</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre mårfältmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epirrhoe hastulata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hübner, 1790)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601042</v>
+        <v>600995</v>
       </c>
       <c r="R43" t="n">
-        <v>6276516</v>
+        <v>6276588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5709,17 +5711,27 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2014-06-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5728,34 +5740,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90973717</t>
+          <t>https://artportalen.se/Sighting/70430543</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70552057</v>
+        <v>90973717</v>
       </c>
       <c r="B44" t="n">
-        <v>41623</v>
+        <v>41695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,51 +5774,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>215755</v>
+        <v>215701</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Längsbandad strimmätare</t>
+          <t>Mindre mårfältmätare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Horisme vitalbata</t>
+          <t>Epirrhoe hastulata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hübner, 1790)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>600995</v>
+        <v>601042</v>
       </c>
       <c r="R44" t="n">
-        <v>6276588</v>
+        <v>6276516</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5829,27 +5828,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5858,30 +5847,31 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70552057</t>
+          <t>https://artportalen.se/Sighting/90973717</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>78876600</v>
+        <v>70552057</v>
       </c>
       <c r="B45" t="n">
         <v>41623</v>
@@ -5911,11 +5901,15 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
@@ -5925,17 +5919,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601040</v>
+        <v>600995</v>
       </c>
       <c r="R45" t="n">
-        <v>6276621</v>
+        <v>6276588</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5959,22 +5953,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5983,31 +5977,30 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876600</t>
+          <t>https://artportalen.se/Sighting/70552057</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>101765510</v>
+        <v>78876600</v>
       </c>
       <c r="B46" t="n">
         <v>41623</v>
@@ -6035,29 +6028,33 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601080</v>
+        <v>601040</v>
       </c>
       <c r="R46" t="n">
-        <v>6276524</v>
+        <v>6276621</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6081,12 +6078,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6102,24 +6109,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765510</t>
+          <t>https://artportalen.se/Sighting/78876600</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111198338</v>
+        <v>101765510</v>
       </c>
       <c r="B47" t="n">
         <v>41623</v>
@@ -6147,33 +6154,29 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601041</v>
+        <v>601080</v>
       </c>
       <c r="R47" t="n">
-        <v>6276563</v>
+        <v>6276524</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6197,22 +6200,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>22:58</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>22:58</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6221,33 +6214,34 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111198338</t>
+          <t>https://artportalen.se/Sighting/101765510</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15750722</v>
+        <v>111198338</v>
       </c>
       <c r="B48" t="n">
-        <v>41655</v>
+        <v>41623</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6255,21 +6249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>215768</v>
+        <v>215755</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Längsbandad strimmätare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Horisme vitalbata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6277,11 +6271,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -6289,17 +6282,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>600995</v>
+        <v>601041</v>
       </c>
       <c r="R48" t="n">
-        <v>6276588</v>
+        <v>6276563</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6323,12 +6316,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2013-07-29</t>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2013-07-30</t>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6343,24 +6346,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15750722</t>
+          <t>https://artportalen.se/Sighting/111198338</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91021113</v>
+        <v>15750722</v>
       </c>
       <c r="B49" t="n">
         <v>41655</v>
@@ -6388,22 +6391,31 @@
           <t>(Hufnagel, 1767)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>601042</v>
+        <v>600995</v>
       </c>
       <c r="R49" t="n">
-        <v>6276516</v>
+        <v>6276588</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6425,17 +6437,17 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2013-07-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6444,34 +6456,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91021113</t>
+          <t>https://artportalen.se/Sighting/15750722</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70552066</v>
+        <v>91021113</v>
       </c>
       <c r="B50" t="n">
-        <v>41579</v>
+        <v>41655</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6479,51 +6490,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>215804</v>
+        <v>215768</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glimmalmätare</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Eupithecia venosata</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>600995</v>
+        <v>601042</v>
       </c>
       <c r="R50" t="n">
-        <v>6276588</v>
+        <v>6276516</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6545,27 +6544,17 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6574,33 +6563,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70552066</t>
+          <t>https://artportalen.se/Sighting/91021113</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101765489</v>
+        <v>70552066</v>
       </c>
       <c r="B51" t="n">
-        <v>42417</v>
+        <v>41579</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6608,46 +6598,54 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>215920</v>
+        <v>215804</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Glimmalmätare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Eupithecia venosata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601080</v>
+        <v>600995</v>
       </c>
       <c r="R51" t="n">
-        <v>6276524</v>
+        <v>6276588</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6671,12 +6669,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2014-07-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6685,51 +6693,50 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765489</t>
+          <t>https://artportalen.se/Sighting/70552066</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101765499</v>
+        <v>101765489</v>
       </c>
       <c r="B52" t="n">
-        <v>42696</v>
+        <v>42417</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>216169</v>
+        <v>215920</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gulbrunt nejlikfly</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hadena perplexa</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6815,56 +6822,60 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765499</t>
+          <t>https://artportalen.se/Sighting/101765489</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2923897</v>
+        <v>101765499</v>
       </c>
       <c r="B53" t="n">
-        <v>99096</v>
+        <v>42696</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>216169</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gulbrunt nejlikfly</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hadena perplexa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601120</v>
+        <v>601080</v>
       </c>
       <c r="R53" t="n">
-        <v>6276584</v>
+        <v>6276524</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6891,12 +6902,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6905,39 +6916,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>f.d. banvall, kalkrik sand</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2923897</t>
+          <t>https://artportalen.se/Sighting/101765499</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>60558553</v>
+        <v>2923897</v>
       </c>
       <c r="B54" t="n">
         <v>99096</v>
@@ -6966,19 +6969,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601112</v>
+        <v>601120</v>
       </c>
       <c r="R54" t="n">
-        <v>6276479</v>
+        <v>6276584</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7000,22 +7005,17 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>de är verkligen annorlunda mot andra i mittlandet, lite klorofyll, tanigare luden, ljusa blommor etc.</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7026,16 +7026,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>f.d. banvall, kalkrik sand</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -7045,13 +7050,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60558553</t>
+          <t>https://artportalen.se/Sighting/2923897</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>72341660</v>
+        <v>60558553</v>
       </c>
       <c r="B55" t="n">
         <v>99096</v>
@@ -7081,23 +7086,18 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dörby tallskog, nära sandheden, Öl</t>
+          <t>Gårdby sandhed NO, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601129</v>
+        <v>601112</v>
       </c>
       <c r="R55" t="n">
-        <v>6276608</v>
+        <v>6276479</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7119,17 +7119,22 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>de är verkligen annorlunda mot andra i mittlandet, lite klorofyll, tanigare luden, ljusa blommor etc.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7138,19 +7143,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7160,13 +7164,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72341660</t>
+          <t>https://artportalen.se/Sighting/60558553</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102606674</v>
+        <v>72341660</v>
       </c>
       <c r="B56" t="n">
         <v>99096</v>
@@ -7198,24 +7202,24 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, nära sandheden, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>601135</v>
+        <v>601129</v>
       </c>
       <c r="R56" t="n">
-        <v>6276471</v>
+        <v>6276608</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7234,17 +7238,17 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7257,84 +7261,80 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Barrskog (gles) på sand</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Anders Svenson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>Botanikdagarna 2022 på Öland</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102606674</t>
+          <t>https://artportalen.se/Sighting/72341660</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16768534</v>
+        <v>102606674</v>
       </c>
       <c r="B57" t="n">
-        <v>109814</v>
+        <v>99096</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220204</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gårdby sandhed norr, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>601064</v>
+        <v>601135</v>
       </c>
       <c r="R57" t="n">
-        <v>6276544</v>
+        <v>6276471</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7353,17 +7353,17 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7372,39 +7372,40 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>Barrskog (gles) på sand</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Jan Yngve Andersson, Anders Svenson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Botanikdagarna 2022 på Öland</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16768534</t>
+          <t>https://artportalen.se/Sighting/102606674</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>53995374</v>
+        <v>16768534</v>
       </c>
       <c r="B58" t="n">
         <v>109814</v>
@@ -7442,14 +7443,14 @@
       <c r="L58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gårdby sandhed N, Öl</t>
+          <t>Gårdby sandhed norr, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>601065</v>
+        <v>601064</v>
       </c>
       <c r="R58" t="n">
-        <v>6276542</v>
+        <v>6276544</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7476,12 +7477,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7495,18 +7496,18 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Tallskogsbryn</t>
+          <t>skogsväg</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7516,16 +7517,16 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53995374</t>
+          <t>https://artportalen.se/Sighting/16768534</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124923374</v>
+        <v>53995374</v>
       </c>
       <c r="B59" t="n">
-        <v>109815</v>
+        <v>109814</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7551,21 +7552,23 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed N, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>601029</v>
+        <v>601065</v>
       </c>
       <c r="R59" t="n">
-        <v>6276548</v>
+        <v>6276542</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7587,27 +7590,17 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2015-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2015-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7618,28 +7611,37 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Tallskogsbryn</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124923374</t>
+          <t>https://artportalen.se/Sighting/53995374</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124946986</v>
+        <v>124923374</v>
       </c>
       <c r="B60" t="n">
         <v>109815</v>
@@ -7668,24 +7670,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gårdby sandhed norr, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600964</v>
+        <v>601029</v>
       </c>
       <c r="R60" t="n">
-        <v>6276616</v>
+        <v>6276548</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7707,7 +7706,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7715,47 +7714,51 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>öppen sand vid körväg</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Stefan Svenaeus, Heléne Wertwein Haavikko, Irene Järlebring, Lars Rigbäck, Bo Andersson, Natalie Henriksson Osbeck, Tommy Carlström, Mats Blomstedt, Ingela Carlström, Anders Waldenström, Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946986</t>
+          <t>https://artportalen.se/Sighting/124923374</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125873636</v>
+        <v>124946986</v>
       </c>
       <c r="B61" t="n">
         <v>109815</v>
@@ -7784,16 +7787,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed norr, Öl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>601097</v>
+        <v>600964</v>
       </c>
       <c r="R61" t="n">
-        <v>6276506</v>
+        <v>6276616</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7815,17 +7826,17 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7834,33 +7845,39 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>öppen sand vid körväg</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Stefan Svenaeus, Heléne Wertwein Haavikko, Irene Järlebring, Lars Rigbäck, Bo Andersson, Natalie Henriksson Osbeck, Tommy Carlström, Mats Blomstedt, Ingela Carlström, Anders Waldenström, Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125873636</t>
+          <t>https://artportalen.se/Sighting/124946986</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>72341663</v>
+        <v>125873636</v>
       </c>
       <c r="B62" t="n">
-        <v>107516</v>
+        <v>109815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,16 +7885,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7886,20 +7903,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Dörby tallskog, nära sandheden, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>601129</v>
+        <v>601097</v>
       </c>
       <c r="R62" t="n">
-        <v>6276608</v>
+        <v>6276506</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7921,17 +7934,17 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7940,35 +7953,30 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72341663</t>
+          <t>https://artportalen.se/Sighting/125873636</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>90968272</v>
+        <v>72341663</v>
       </c>
       <c r="B63" t="n">
         <v>107516</v>
@@ -7997,16 +8005,20 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Dörby tallskog, nära sandheden, Öl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>601036</v>
+        <v>601129</v>
       </c>
       <c r="R63" t="n">
-        <v>6276547</v>
+        <v>6276608</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8028,17 +8040,17 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8047,42 +8059,38 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Betad kalkgräsmark</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eric Lundén</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cassandra Hallman</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90968272</t>
+          <t>https://artportalen.se/Sighting/72341663</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>87452574</v>
+        <v>90968272</v>
       </c>
       <c r="B64" t="n">
-        <v>107060</v>
+        <v>107516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8090,16 +8098,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8108,24 +8116,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gårdby sandhed N, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>601010</v>
+        <v>601036</v>
       </c>
       <c r="R64" t="n">
-        <v>6276582</v>
+        <v>6276547</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8147,17 +8147,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8166,38 +8166,42 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Betad kalkgräsmark</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Per Ahlgren</t>
+          <t>Eric Lundén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Stefan Björn, Per Ahlgren</t>
+          <t>Cassandra Hallman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87452574</t>
+          <t>https://artportalen.se/Sighting/90968272</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>60558453</v>
+        <v>87452574</v>
       </c>
       <c r="B65" t="n">
-        <v>98050</v>
+        <v>107060</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8205,45 +8209,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222112</v>
+        <v>221903</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO, Öl</t>
+          <t>Gårdby sandhed N, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>601112</v>
+        <v>601010</v>
       </c>
       <c r="R65" t="n">
-        <v>6276479</v>
+        <v>6276582</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8265,17 +8266,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8284,18 +8285,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Per Ahlgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Stefan Björn, Per Ahlgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8305,16 +8307,16 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60558453</t>
+          <t>https://artportalen.se/Sighting/87452574</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5141664</v>
+        <v>60558453</v>
       </c>
       <c r="B66" t="n">
-        <v>100797</v>
+        <v>98050</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8322,34 +8324,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222617</v>
+        <v>222112</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Gårdby sandhed NO, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>601093</v>
+        <v>601112</v>
       </c>
       <c r="R66" t="n">
-        <v>6276554</v>
+        <v>6276479</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8371,22 +8384,17 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8397,21 +8405,16 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8421,13 +8424,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5141664</t>
+          <t>https://artportalen.se/Sighting/60558453</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>54136165</v>
+        <v>5141664</v>
       </c>
       <c r="B67" t="n">
         <v>100797</v>
@@ -8456,26 +8459,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO., Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>601088</v>
+        <v>601093</v>
       </c>
       <c r="R67" t="n">
-        <v>6276505</v>
+        <v>6276554</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8494,17 +8490,22 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8515,16 +8516,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>tallskog med lövinslag</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8534,16 +8540,16 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54136165</t>
+          <t>https://artportalen.se/Sighting/5141664</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124946779</v>
+        <v>54136165</v>
       </c>
       <c r="B68" t="n">
-        <v>100798</v>
+        <v>100797</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8570,22 +8576,25 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR, Öl</t>
+          <t>Gårdby sandhed NO., Öl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>601035</v>
+        <v>601088</v>
       </c>
       <c r="R68" t="n">
-        <v>6276550</v>
+        <v>6276505</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8609,12 +8618,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8623,61 +8632,59 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>betad sandgräshed</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946779</t>
+          <t>https://artportalen.se/Sighting/54136165</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125545586</v>
+        <v>124946779</v>
       </c>
       <c r="B69" t="n">
-        <v>101345</v>
+        <v>100798</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222886</v>
+        <v>222617</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8687,17 +8694,17 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Galgrör, Galgrör, Öl</t>
+          <t>Gårdby sandhed NR, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>601082</v>
+        <v>601035</v>
       </c>
       <c r="R69" t="n">
-        <v>6276507</v>
+        <v>6276550</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8721,22 +8728,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8745,72 +8742,81 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>betad sandgräshed</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist, Andreas Källman</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125545586</t>
+          <t>https://artportalen.se/Sighting/124946779</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6181704</v>
+        <v>125545586</v>
       </c>
       <c r="B70" t="n">
-        <v>107062</v>
+        <v>101345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224354</v>
+        <v>222886</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Galgrör, Galgrör, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>601114</v>
+        <v>601082</v>
       </c>
       <c r="R70" t="n">
-        <v>6276570</v>
+        <v>6276507</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8829,22 +8835,27 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8855,84 +8866,67 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Andreas Lundqvist, Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6181704</t>
+          <t>https://artportalen.se/Sighting/125545586</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>62497754</v>
+        <v>6181704</v>
       </c>
       <c r="B71" t="n">
-        <v>13027</v>
+        <v>107062</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>236198</v>
+        <v>224354</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vanlig axveronika</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Villa longicornis</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Lyneborg, 1965</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>Veronica spicata subsp. spicata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, väg N om, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>600989</v>
+        <v>601114</v>
       </c>
       <c r="R71" t="n">
-        <v>6276600</v>
+        <v>6276570</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8959,12 +8953,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8978,32 +8977,152 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>sandig brukningsväg</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>Jan Edelsjö</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>NHRS-JEDS000006494</t>
+          <t>tallskog med lövinslag</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6181704</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>62497754</v>
+      </c>
+      <c r="B72" t="n">
+        <v>13027</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>236198</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Villa longicornis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Lyneborg, 1965</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gårdby sandhed, väg N om, Öl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>600989</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6276600</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>sandig brukningsväg</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
           <t>Jan Edelsjö</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>NHRS-JEDS000006494</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jan Edelsjö</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
         <is>
           <t>Jan Edelsjö, Niklas Lönnell, Johan Nilsson, Jonas Sandström</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62497754</t>
         </is>
@@ -9081,6 +9200,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91551</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91556</v>
+        <v>91566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91566</v>
+        <v>91567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91567</v>
+        <v>91570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91570</v>
+        <v>91572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91572</v>
+        <v>91577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91577</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91590</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>137226892</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
